--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_224_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_224_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1923,10 +1923,10 @@
         <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>132</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4292,7 +4292,7 @@
         <v>18</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>3</v>
@@ -4684,7 +4684,7 @@
         <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>8</v>
@@ -5468,7 +5468,7 @@
         <v>12</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>15</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>109</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_224_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_224_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -854,17 +854,17 @@
         <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,10 +5284,10 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5516,18 +5516,18 @@
         <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6600,14 +6600,14 @@
         <v>2</v>
       </c>
       <c r="X47" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y47" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="AA47" t="n">
@@ -6636,22 +6636,22 @@
         <v>5</v>
       </c>
       <c r="AH47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="AJ47" t="n">
         <v>11</v>
       </c>
       <c r="AK47" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
